--- a/DataTables/Datas/#VSCharacter.xlsx
+++ b/DataTables/Datas/#VSCharacter.xlsx
@@ -558,7 +558,7 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>0.15</v>
+        <v>0.225</v>
       </c>
       <c r="G4" t="n">
         <v>0.4</v>
